--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_35.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_35.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ExamPass?</t>
+          <t>Response</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Diligence</t>
+          <t>IV2</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.3992733747031435</v>
+        <v>1.150570144623932</v>
       </c>
       <c r="C2">
-        <v>-0.7359042907144986</v>
+        <v>-0.5571394994424888</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.1969358012470944</v>
+        <v>-0.1502253984928243</v>
       </c>
       <c r="C3">
-        <v>-0.260613486453089</v>
+        <v>-0.1636992755293741</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.9082929998712477</v>
+        <v>0.1432135622007547</v>
       </c>
       <c r="C4">
-        <v>0.3241739444942093</v>
+        <v>0.4114785047697057</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.8419202661914378</v>
+        <v>-1.557523453200593</v>
       </c>
       <c r="C5">
-        <v>-0.7835654988140364</v>
+        <v>-0.8312059738066498</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1054676534180572</v>
+        <v>0.2566958511887716</v>
       </c>
       <c r="C6">
-        <v>0.4092627719101227</v>
+        <v>-0.4170254777959407</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.5119081197861849</v>
+        <v>0.1478250227779115</v>
       </c>
       <c r="C7">
-        <v>1.539258831350475</v>
+        <v>0.6366401419439891</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-1.119393138452122</v>
+        <v>-0.5942530204589156</v>
       </c>
       <c r="C8">
-        <v>-0.4520718401977297</v>
+        <v>-0.8979094648484323</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.259024987251619</v>
+        <v>-0.06331170779072462</v>
       </c>
       <c r="C9">
-        <v>-1.986864132004239</v>
+        <v>0.3531107834529519</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.343828813104133</v>
+        <v>0.5866187721574274</v>
       </c>
       <c r="C10">
-        <v>1.001648439811759</v>
+        <v>0.6404844310937211</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.7166788637518119</v>
+        <v>-0.5809642351292756</v>
       </c>
       <c r="C11">
-        <v>-0.5395587818608554</v>
+        <v>-2.679916274696973</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.25881688212549</v>
+        <v>1.062358751165796</v>
       </c>
       <c r="C12">
-        <v>-1.292608646128211</v>
+        <v>0.8045820011789644</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.161416589079712</v>
+        <v>-0.6730956720195788</v>
       </c>
       <c r="C13">
-        <v>-0.4927666769962745</v>
+        <v>-0.1462964553335402</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.3445820107017977</v>
+        <v>0.08404400492571681</v>
       </c>
       <c r="C14">
-        <v>-0.034126663379682</v>
+        <v>-0.4549754623752728</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.04787641480989627</v>
+        <v>0.09603385759934364</v>
       </c>
       <c r="C15">
-        <v>0.1766332621002479</v>
+        <v>0.5750557128006522</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.002615856489447</v>
+        <v>0.2963154933957181</v>
       </c>
       <c r="C16">
-        <v>0.62003729823609</v>
+        <v>0.09334966634884491</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.01227371043131894</v>
+        <v>0.4879229347023995</v>
       </c>
       <c r="C17">
-        <v>-1.116402577570832</v>
+        <v>-1.168844935142276</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.6907961062879183</v>
+        <v>-0.06573863507903499</v>
       </c>
       <c r="C18">
-        <v>-0.004812057782892454</v>
+        <v>-0.4171853022574309</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-1.019217250040131</v>
+        <v>-0.1873897570119101</v>
       </c>
       <c r="C19">
-        <v>1.284910367347323</v>
+        <v>-2.099543375635372</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.122190181846827</v>
+        <v>0.1768651185973478</v>
       </c>
       <c r="C20">
-        <v>-0.07318081841463542</v>
+        <v>-0.1269234555034273</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.8652084830642611</v>
+        <v>0.07697929115751337</v>
       </c>
       <c r="C21">
-        <v>0.5684305327256999</v>
+        <v>0.111052705658766</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.9470065415506753</v>
+        <v>0.9500678515253391</v>
       </c>
       <c r="C22">
-        <v>0.6317379394279932</v>
+        <v>-0.1382683949517082</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.5028317855574481</v>
+        <v>-1.557032218691908</v>
       </c>
       <c r="C23">
-        <v>-2.883617964350875</v>
+        <v>0.5054653638012188</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.063372838898809</v>
+        <v>0.3913917335022189</v>
       </c>
       <c r="C24">
-        <v>-0.4563389998853072</v>
+        <v>0.6856225266059908</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.1994120505740557</v>
+        <v>-0.8920766625055373</v>
       </c>
       <c r="C25">
-        <v>-0.4553874839848692</v>
+        <v>-0.8963738435709999</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.2273355994127199</v>
+        <v>-1.476502071608068</v>
       </c>
       <c r="C26">
-        <v>1.260416099979915</v>
+        <v>-2.124215632066711</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.1821820157164034</v>
+        <v>1.300806558046401</v>
       </c>
       <c r="C27">
-        <v>-0.1396823215917297</v>
+        <v>1.085989675662941</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.7557314665395389</v>
+        <v>1.258765302541289</v>
       </c>
       <c r="C28">
-        <v>0.08149946725095494</v>
+        <v>1.580296430861888</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.5595812632950332</v>
+        <v>-2.715766362966528</v>
       </c>
       <c r="C29">
-        <v>0.8550262218284268</v>
+        <v>-2.264488521168876</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.1655382177198654</v>
+        <v>0.9571115120305906</v>
       </c>
       <c r="C30">
-        <v>-0.7523137777709508</v>
+        <v>0.08377629866553304</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.3545164142757118</v>
+        <v>0.2492414678281386</v>
       </c>
       <c r="C31">
-        <v>-0.6585504507412623</v>
+        <v>0.01149410428524389</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.7781155104436206</v>
+        <v>2.195771358514907</v>
       </c>
       <c r="C32">
-        <v>-0.6069009295162937</v>
+        <v>-0.3501520496091217</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.120829884555334</v>
+        <v>1.785459653031619</v>
       </c>
       <c r="C33">
-        <v>0.4345500625477601</v>
+        <v>1.832937649665983</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.0830755268411917</v>
+        <v>0.1685182355099293</v>
       </c>
       <c r="C34">
-        <v>0.4233279944251368</v>
+        <v>0.4104432910756775</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.5933420564553801</v>
+        <v>0.4344379249344852</v>
       </c>
       <c r="C35">
-        <v>0.210375426092632</v>
+        <v>-0.7552153722726695</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.993805702868499</v>
+        <v>0.6312681658471235</v>
       </c>
       <c r="C36">
-        <v>-0.8994884621613618</v>
+        <v>0.6469387066484693</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.3538842131948799</v>
+        <v>-0.206433236475649</v>
       </c>
       <c r="C37">
-        <v>-0.07473913854995876</v>
+        <v>-1.402797749331687</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.73549618596474</v>
+        <v>-0.4499293965182279</v>
       </c>
       <c r="C38">
-        <v>-1.970622803408761</v>
+        <v>-1.005706706651817</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.6422257756094535</v>
+        <v>-0.3167632811066043</v>
       </c>
       <c r="C39">
-        <v>-0.5866124523563871</v>
+        <v>-0.4906523850578429</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.05556810629085167</v>
+        <v>1.073624869102829</v>
       </c>
       <c r="C40">
-        <v>-0.1046076045362144</v>
+        <v>0.9024529862313189</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.9039418784796279</v>
+        <v>-0.3035483837017875</v>
       </c>
       <c r="C41">
-        <v>-1.188968754127524</v>
+        <v>1.398051584448677</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.4383694045198824</v>
+        <v>0.301789907730982</v>
       </c>
       <c r="C42">
-        <v>0.3591168515004901</v>
+        <v>0.893670394663944</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.4146656293881629</v>
+        <v>-1.84259395901279</v>
       </c>
       <c r="C43">
-        <v>-0.4186855232883868</v>
+        <v>-0.6390495990852563</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.4088360350095432</v>
+        <v>1.009523487820551</v>
       </c>
       <c r="C44">
-        <v>0.6300345447752115</v>
+        <v>0.8004469976764592</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>1.107906557560213</v>
+        <v>-1.161290866760178</v>
       </c>
       <c r="C45">
-        <v>-0.1011888499287402</v>
+        <v>-0.1402023009769778</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.3766629311215208</v>
+        <v>-0.2275946215137731</v>
       </c>
       <c r="C46">
-        <v>-1.184357685092786</v>
+        <v>-0.2713113731254815</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.4200196105232742</v>
+        <v>0.3648488122667338</v>
       </c>
       <c r="C47">
-        <v>-0.4093364337336068</v>
+        <v>-0.9397339822404591</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.084406306227275</v>
+        <v>0.06351234647104501</v>
       </c>
       <c r="C48">
-        <v>0.965492823744974</v>
+        <v>0.2757170766511864</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.08651026603676301</v>
+        <v>-0.8346879523047209</v>
       </c>
       <c r="C49">
-        <v>-0.6073329201392151</v>
+        <v>1.42570929997909</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.001224314469343</v>
+        <v>-1.073840187163396</v>
       </c>
       <c r="C50">
-        <v>-0.6054204042041313</v>
+        <v>-1.497179197342595</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.8115808450755974</v>
+        <v>0.2466693769338612</v>
       </c>
       <c r="C51">
-        <v>1.019872828464981</v>
+        <v>0.2257074252179688</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>-0.690474303473023</v>
+      </c>
+      <c r="C52">
+        <v>-0.7685427060738463</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>-1.747838385063126</v>
+      </c>
+      <c r="C53">
+        <v>0.8619681757478008</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>0.3012059429411412</v>
+      </c>
+      <c r="C54">
+        <v>0.02049616608453535</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>-0.6167075427262921</v>
+      </c>
+      <c r="C55">
+        <v>-1.225444039049635</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>-1.756319725419407</v>
+      </c>
+      <c r="C56">
+        <v>-0.1875316491450354</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>-0.9465303653381089</v>
+      </c>
+      <c r="C57">
+        <v>-0.7615498575175634</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>-0.5447632988502391</v>
+      </c>
+      <c r="C58">
+        <v>-1.620816359567716</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>-0.06462581701837684</v>
+      </c>
+      <c r="C59">
+        <v>0.318508148891912</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>-0.5954733137351949</v>
+      </c>
+      <c r="C60">
+        <v>1.378768613069436</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.7152538194225718</v>
+      </c>
+      <c r="C61">
+        <v>-0.8938449659289623</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>-1.127122075249172</v>
+      </c>
+      <c r="C62">
+        <v>-0.7423586933856553</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>0.3486427798990279</v>
+      </c>
+      <c r="C63">
+        <v>0.8033273299617147</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>-0.3329312463877055</v>
+      </c>
+      <c r="C64">
+        <v>-0.4739850832387827</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0.8151743687248739</v>
+      </c>
+      <c r="C65">
+        <v>0.2311040184939901</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>-0.06315366307210547</v>
+      </c>
+      <c r="C66">
+        <v>1.149557751730193</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>0.03385580982299128</v>
+      </c>
+      <c r="C67">
+        <v>-1.519941010523207</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>-1.456987879072733</v>
+      </c>
+      <c r="C68">
+        <v>0.1008666322862645</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>-1.674500431759777</v>
+      </c>
+      <c r="C69">
+        <v>-0.2947656967785419</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>0.90657991576374</v>
+      </c>
+      <c r="C70">
+        <v>0.3531493058770425</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>-1.054276883517295</v>
+      </c>
+      <c r="C71">
+        <v>0.58030235505464</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>0.2824676855920953</v>
+      </c>
+      <c r="C72">
+        <v>-0.3054040342317784</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>-0.7589061205649741</v>
+      </c>
+      <c r="C73">
+        <v>-0.6557877276059909</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>0.4970233491324796</v>
+      </c>
+      <c r="C74">
+        <v>0.8228490255399993</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>1.892294279190181</v>
+      </c>
+      <c r="C75">
+        <v>-0.428019589596756</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>-0.08678062207468498</v>
+      </c>
+      <c r="C76">
+        <v>1.18780708442809</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-1.174744942544264</v>
+      </c>
+      <c r="C77">
+        <v>0.03184907477647225</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>-0.3570002741760371</v>
+      </c>
+      <c r="C78">
+        <v>-0.9630195306291135</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>-0.7179423913020495</v>
+      </c>
+      <c r="C79">
+        <v>-1.468055973689149</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>-0.7394622156069371</v>
+      </c>
+      <c r="C80">
+        <v>-0.2630782106710436</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>0.02734033299032503</v>
+      </c>
+      <c r="C81">
+        <v>-0.02998260142239532</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>1.42551074060639</v>
+      </c>
+      <c r="C82">
+        <v>0.2257997843445093</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>0.4492918032458988</v>
+      </c>
+      <c r="C83">
+        <v>-0.7077393256625959</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>-0.2986271111272751</v>
+      </c>
+      <c r="C84">
+        <v>-0.722589320757435</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>0.1158380121350411</v>
+      </c>
+      <c r="C85">
+        <v>2.035410585709449</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>1.512405822614517</v>
+      </c>
+      <c r="C86">
+        <v>1.507450534065883</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>0.52515756759788</v>
+      </c>
+      <c r="C87">
+        <v>1.347239593067347</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>-0.2496730654300049</v>
+      </c>
+      <c r="C88">
+        <v>-0.4765569950055477</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>1.919647442467447</v>
+      </c>
+      <c r="C89">
+        <v>0.8742589704152055</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>0.8459306559921862</v>
+      </c>
+      <c r="C90">
+        <v>1.007752551563559</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>1.293365693727196</v>
+      </c>
+      <c r="C91">
+        <v>1.549577216743454</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>0.8175484092636499</v>
+      </c>
+      <c r="C92">
+        <v>0.1927232971696209</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>-1.527732557226933</v>
+      </c>
+      <c r="C93">
+        <v>-1.979483661227522</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>-1.23416672428248</v>
+      </c>
+      <c r="C94">
+        <v>-0.7946035157982591</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>-0.2881560775969939</v>
+      </c>
+      <c r="C95">
+        <v>1.183047704333435</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>-0.177821308608771</v>
+      </c>
+      <c r="C96">
+        <v>-0.08770422401551914</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>0.9986806430492998</v>
+      </c>
+      <c r="C97">
+        <v>0.5813127917709483</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>0.670292958229826</v>
+      </c>
+      <c r="C98">
+        <v>-1.17281016667421</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>0.3284205562705638</v>
+      </c>
+      <c r="C99">
+        <v>0.3226114551613737</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>-0.6328178814207229</v>
+      </c>
+      <c r="C100">
+        <v>-1.566938775834638</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>-1.525685117376225</v>
+      </c>
+      <c r="C101">
+        <v>0.1572524308949377</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-1.39114059830068</v>
+      </c>
+      <c r="C102">
+        <v>-1.031329167973986</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-1.387726467804816</v>
+      </c>
+      <c r="C103">
+        <v>-0.1929373193221619</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>0.3804319746567883</v>
+      </c>
+      <c r="C104">
+        <v>-0.08942220448944371</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>0.827538099207162</v>
+      </c>
+      <c r="C105">
+        <v>1.104098333550086</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-0.8497682029642624</v>
+      </c>
+      <c r="C106">
+        <v>0.3984576838093061</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-0.5725548285708425</v>
+      </c>
+      <c r="C107">
+        <v>-2.449665486582653</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-1.125439657994396</v>
+      </c>
+      <c r="C108">
+        <v>1.275691062128224</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>-1.528562971580939</v>
+      </c>
+      <c r="C109">
+        <v>-0.7789681476124957</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>1.094799284536458</v>
+      </c>
+      <c r="C110">
+        <v>-0.08469689882515441</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>-1.311269445492137</v>
+      </c>
+      <c r="C111">
+        <v>-0.7111794585433717</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>-0.2448204003122629</v>
+      </c>
+      <c r="C112">
+        <v>-0.499667623402442</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-0.2135229914831088</v>
+      </c>
+      <c r="C113">
+        <v>-0.7662553979074682</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>0.5752757974380337</v>
+      </c>
+      <c r="C114">
+        <v>0.3567568247738677</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>0.3357813561263662</v>
+      </c>
+      <c r="C115">
+        <v>0.323953799556399</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>0.8180698543263689</v>
+      </c>
+      <c r="C116">
+        <v>0.6537063280976322</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>0.9728928364250005</v>
+      </c>
+      <c r="C117">
+        <v>1.600415713828287</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>0.4626964188327842</v>
+      </c>
+      <c r="C118">
+        <v>0.8612492237031556</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>-0.6980872702573676</v>
+      </c>
+      <c r="C119">
+        <v>-0.1059964300278021</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>0.9906111396596817</v>
+      </c>
+      <c r="C120">
+        <v>-0.612356592114085</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-0.2002988361532941</v>
+      </c>
+      <c r="C121">
+        <v>-0.8302084196002961</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.03276571910670978</v>
+      </c>
+      <c r="C122">
+        <v>-0.1121922843878648</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.2807156604901072</v>
+      </c>
+      <c r="C123">
+        <v>0.3558625227159283</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-0.7962106461386448</v>
+      </c>
+      <c r="C124">
+        <v>-1.287128498311785</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.8501808388147775</v>
+      </c>
+      <c r="C125">
+        <v>-0.7793460181325109</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-0.4056387565372631</v>
+      </c>
+      <c r="C126">
+        <v>0.9211292098901949</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>0.04353684706596895</v>
+      </c>
+      <c r="C127">
+        <v>-0.6629461915710462</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>0.2521689419733006</v>
+      </c>
+      <c r="C128">
+        <v>0.8903529131529812</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.007267774972836248</v>
+      </c>
+      <c r="C129">
+        <v>0.7807441418579802</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>0.1267226957706892</v>
+      </c>
+      <c r="C130">
+        <v>-1.318466743423261</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-1.656773619599779</v>
+      </c>
+      <c r="C131">
+        <v>-0.5888364720772445</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>1.595757289780317</v>
+      </c>
+      <c r="C132">
+        <v>1.802550072052181</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.277604046289241</v>
+      </c>
+      <c r="C133">
+        <v>-1.823716687973611</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-1.245379345798528</v>
+      </c>
+      <c r="C134">
+        <v>-0.07453530918530821</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.19793463134063</v>
+      </c>
+      <c r="C135">
+        <v>-0.2487332569336239</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-0.3954947247166873</v>
+      </c>
+      <c r="C136">
+        <v>-0.3042320994060261</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.2914376603602367</v>
+      </c>
+      <c r="C137">
+        <v>-2.247270377267162</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>0.1193743803210116</v>
+      </c>
+      <c r="C138">
+        <v>-0.4086361016629789</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.05452422614431909</v>
+      </c>
+      <c r="C139">
+        <v>0.1672669930894183</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.4180168044745359</v>
+      </c>
+      <c r="C140">
+        <v>0.2813543329874166</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>-0.1188895213776009</v>
+      </c>
+      <c r="C141">
+        <v>0.04191921503511649</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>1.2558895022394</v>
+      </c>
+      <c r="C142">
+        <v>-0.3036745653624731</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-0.4970075307189778</v>
+      </c>
+      <c r="C143">
+        <v>0.5737804428788897</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-1.15115265284692</v>
+      </c>
+      <c r="C144">
+        <v>0.4413918571285662</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>1.504183878459187</v>
+      </c>
+      <c r="C145">
+        <v>0.9173910870992721</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.1682426356719271</v>
+      </c>
+      <c r="C146">
+        <v>0.3759574745736524</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-0.5710745661109361</v>
+      </c>
+      <c r="C147">
+        <v>-0.1087893649516832</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.6492158320216026</v>
+      </c>
+      <c r="C148">
+        <v>-0.3726505410569909</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>1.790920665580447</v>
+      </c>
+      <c r="C149">
+        <v>1.654285320253029</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>-0.02590055606993822</v>
+      </c>
+      <c r="C150">
+        <v>-0.2021870780008525</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>2.317193575132138</v>
+      </c>
+      <c r="C151">
+        <v>-0.7702286853141278</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>0.0634604364821923</v>
+      </c>
+      <c r="C152">
+        <v>-1.461128651549623</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>0.7666091577412845</v>
+      </c>
+      <c r="C153">
+        <v>2.726148020891046</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>0.2563533442706403</v>
+      </c>
+      <c r="C154">
+        <v>0.5255657492886203</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.463176021518127</v>
+      </c>
+      <c r="C155">
+        <v>-0.3811639993944266</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>-1.260189053923745</v>
+      </c>
+      <c r="C156">
+        <v>-1.322383270492988</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>0.2188336941502704</v>
+      </c>
+      <c r="C157">
+        <v>1.478759493633269</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>-1.289155694018113</v>
+      </c>
+      <c r="C158">
+        <v>-0.9257242690026406</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>0.2977557723400787</v>
+      </c>
+      <c r="C159">
+        <v>0.6566819402621774</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.8604055469773034</v>
+      </c>
+      <c r="C160">
+        <v>0.2400343372215574</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-1.407046524663916</v>
+      </c>
+      <c r="C161">
+        <v>0.08627294708181388</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>0.6596389146624353</v>
+      </c>
+      <c r="C162">
+        <v>0.9110927416180086</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>1.065230719605629</v>
+      </c>
+      <c r="C163">
+        <v>0.2294733259600159</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>1.182781494565586</v>
+      </c>
+      <c r="C164">
+        <v>0.7650330210341811</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-0.04751073792355318</v>
+      </c>
+      <c r="C165">
+        <v>-0.8014778208744374</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-1.226617460924145</v>
+      </c>
+      <c r="C166">
+        <v>1.800100686154675</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-0.1795334869107748</v>
+      </c>
+      <c r="C167">
+        <v>0.9219477892382286</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>1.191587279148118</v>
+      </c>
+      <c r="C168">
+        <v>-0.3843834756888735</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-1.302913632072605</v>
+      </c>
+      <c r="C169">
+        <v>-0.7972147532097222</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>0.07903887948936447</v>
+      </c>
+      <c r="C170">
+        <v>0.5305542454466483</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>0.2253665174361204</v>
+      </c>
+      <c r="C171">
+        <v>-0.321485133235185</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.32290709404189</v>
+      </c>
+      <c r="C172">
+        <v>1.301038813295955</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>-1.483296360000238</v>
+      </c>
+      <c r="C173">
+        <v>-0.2919502290225386</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>1.433149006193119</v>
+      </c>
+      <c r="C174">
+        <v>0.2731513159288463</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>1.999594707210082</v>
+      </c>
+      <c r="C175">
+        <v>0.3017039588356399</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-1.284202022020445</v>
+      </c>
+      <c r="C176">
+        <v>-0.6103974853808946</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>0.746652829978548</v>
+      </c>
+      <c r="C177">
+        <v>1.985921728517675</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.5721871356691862</v>
+      </c>
+      <c r="C178">
+        <v>0.733775878989714</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.6190648831828505</v>
+      </c>
+      <c r="C179">
+        <v>-0.5083348344953944</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>-0.6454233576864395</v>
+      </c>
+      <c r="C180">
+        <v>-0.800539781605048</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>1.303261932857706</v>
+      </c>
+      <c r="C181">
+        <v>0.6258107232518034</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.1877993409274404</v>
+      </c>
+      <c r="C182">
+        <v>0.469490091047726</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>0.2329929248982893</v>
+      </c>
+      <c r="C183">
+        <v>1.291710264940091</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>1.88591509875951</v>
+      </c>
+      <c r="C184">
+        <v>2.448374900212993</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-0.579272846553472</v>
+      </c>
+      <c r="C185">
+        <v>0.3013193599344536</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>1.061673144136786</v>
+      </c>
+      <c r="C186">
+        <v>1.166122063242502</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.4905332591470198</v>
+      </c>
+      <c r="C187">
+        <v>0.5522228976857848</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>0.3094746082322339</v>
+      </c>
+      <c r="C188">
+        <v>0.3278165970068639</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>0.1907296255152824</v>
+      </c>
+      <c r="C189">
+        <v>-1.400576577193804</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>-0.3274059039270263</v>
+      </c>
+      <c r="C190">
+        <v>0.5534194431801966</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>0.8166203664545476</v>
+      </c>
+      <c r="C191">
+        <v>1.911119584605914</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-1.323554942022081</v>
+      </c>
+      <c r="C192">
+        <v>0.152871466355037</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.3426127947741641</v>
+      </c>
+      <c r="C193">
+        <v>-0.9465676839458477</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-0.8348460480147222</v>
+      </c>
+      <c r="C194">
+        <v>0.8308625353724231</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>0.4315056508882237</v>
+      </c>
+      <c r="C195">
+        <v>-0.5431461447262793</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>0.1283876906209759</v>
+      </c>
+      <c r="C196">
+        <v>-0.8004500017765183</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>1.380803293254272</v>
+      </c>
+      <c r="C197">
+        <v>1.314592633812238</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.0812398226266547</v>
+      </c>
+      <c r="C198">
+        <v>0.1852588850281279</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>-0.9623120533983394</v>
+      </c>
+      <c r="C199">
+        <v>-1.033087414975199</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.7825703929471939</v>
+      </c>
+      <c r="C200">
+        <v>0.9434623556528823</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-0.2370764937114961</v>
+      </c>
+      <c r="C201">
+        <v>1.89773481663009</v>
       </c>
     </row>
   </sheetData>
